--- a/server/api/offshore_forecast_api/models/certification_feature_importance.xlsx
+++ b/server/api/offshore_forecast_api/models/certification_feature_importance.xlsx
@@ -448,105 +448,105 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Leg</t>
+          <t>Piles</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2154586613178253</v>
+        <v>0.409345418214798</v>
       </c>
       <c r="C2" t="n">
-        <v>21.54586791992188</v>
+        <v>40.93453598022461</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Panjang (km)</t>
+          <t>Topsides/Deck</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1889186203479767</v>
+        <v>0.2134904861450195</v>
       </c>
       <c r="C3" t="n">
-        <v>18.8918628692627</v>
+        <v>21.34904479980469</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Topsides/Deck</t>
+          <t>Jacket</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1428885161876678</v>
+        <v>0.08554457873106003</v>
       </c>
       <c r="C4" t="n">
-        <v>14.28885269165039</v>
+        <v>8.55445671081543</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Water Depth (meter)</t>
+          <t>Conductor</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1142063438892365</v>
+        <v>0.07624666392803192</v>
       </c>
       <c r="C5" t="n">
-        <v>11.42063522338867</v>
+        <v>7.6246657371521</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Diameter (inch)</t>
+          <t>Leg</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0923905149102211</v>
+        <v>0.0673336461186409</v>
       </c>
       <c r="C6" t="n">
-        <v>9.239051818847656</v>
+        <v>6.733364105224609</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Piles</t>
+          <t>Water Depth (meter)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0835113525390625</v>
+        <v>0.05121593549847603</v>
       </c>
       <c r="C7" t="n">
-        <v>8.351136207580566</v>
+        <v>5.121592998504639</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Conductor</t>
+          <t>Panjang (km)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.08157975971698761</v>
+        <v>0.04963493347167969</v>
       </c>
       <c r="C8" t="n">
-        <v>8.157977104187012</v>
+        <v>4.963492393493652</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Jacket</t>
+          <t>Diameter (inch)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0810462012887001</v>
+        <v>0.04718839377164841</v>
       </c>
       <c r="C9" t="n">
-        <v>8.104620933532715</v>
+        <v>4.718838691711426</v>
       </c>
     </row>
   </sheetData>
